--- a/Team-Data/2008-09/1-22-2008-09.xlsx
+++ b/Team-Data/2008-09/1-22-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>9</v>
@@ -754,13 +821,13 @@
         <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ2" t="n">
         <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
@@ -772,7 +839,7 @@
         <v>12</v>
       </c>
       <c r="AO2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
         <v>18</v>
@@ -784,7 +851,7 @@
         <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
@@ -811,7 +878,7 @@
         <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -858,19 +925,19 @@
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>76.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M3" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="N3" t="n">
         <v>0.381</v>
@@ -879,64 +946,64 @@
         <v>20.6</v>
       </c>
       <c r="P3" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S3" t="n">
         <v>32.1</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U3" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V3" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W3" t="n">
         <v>8.5</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
         <v>23</v>
       </c>
       <c r="AA3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AB3" t="n">
         <v>100.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH3" t="n">
         <v>13</v>
       </c>
       <c r="AI3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -945,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM3" t="n">
         <v>18</v>
@@ -957,7 +1024,7 @@
         <v>5</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ3" t="n">
         <v>12</v>
@@ -981,7 +1048,7 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -993,7 +1060,7 @@
         <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF4" t="n">
         <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
         <v>7</v>
@@ -1133,7 +1200,7 @@
         <v>25</v>
       </c>
       <c r="AN4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
         <v>18</v>
@@ -1169,7 +1236,7 @@
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
         <v>14</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -1207,85 +1274,85 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
         <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>0.405</v>
+        <v>0.419</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J5" t="n">
-        <v>84.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="K5" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L5" t="n">
         <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O5" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="P5" t="n">
-        <v>22.9</v>
+        <v>23.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.798</v>
+        <v>0.796</v>
       </c>
       <c r="R5" t="n">
         <v>11.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U5" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X5" t="n">
         <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.5</v>
+        <v>-3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>19</v>
@@ -1294,13 +1361,13 @@
         <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ5" t="n">
         <v>4</v>
@@ -1312,16 +1379,16 @@
         <v>19</v>
       </c>
       <c r="AM5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN5" t="n">
         <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AP5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1333,13 +1400,13 @@
         <v>13</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW5" t="n">
         <v>13</v>
@@ -1348,19 +1415,19 @@
         <v>5</v>
       </c>
       <c r="AY5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -1389,43 +1456,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="n">
         <v>32</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.821</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J6" t="n">
-        <v>78.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.479</v>
+        <v>0.478</v>
       </c>
       <c r="L6" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M6" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.368</v>
+        <v>0.365</v>
       </c>
       <c r="O6" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="P6" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
         <v>0.756</v>
@@ -1434,40 +1501,40 @@
         <v>10.6</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
         <v>41.5</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="W6" t="n">
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.1</v>
+        <v>100.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.5</v>
+        <v>11.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>4</v>
@@ -1476,13 +1543,13 @@
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1491,25 +1558,25 @@
         <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1518,7 +1585,7 @@
         <v>15</v>
       </c>
       <c r="AU6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV6" t="n">
         <v>7</v>
@@ -1530,16 +1597,16 @@
         <v>3</v>
       </c>
       <c r="AY6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>0.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1961,7 @@
         <v>6</v>
       </c>
       <c r="AY8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ8" t="n">
         <v>24</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -2013,13 +2080,13 @@
         <v>0.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
       </c>
       <c r="AF9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG9" t="n">
         <v>11</v>
@@ -2028,7 +2095,7 @@
         <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ9" t="n">
         <v>18</v>
@@ -2061,10 +2128,10 @@
         <v>14</v>
       </c>
       <c r="AT9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV9" t="n">
         <v>2</v>
@@ -2076,13 +2143,13 @@
         <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
         <v>27</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2286,7 @@
         <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM10" t="n">
         <v>14</v>
@@ -2234,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
         <v>4</v>
@@ -2246,10 +2313,10 @@
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2477,7 @@
         <v>14</v>
       </c>
       <c r="AO11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
@@ -2428,7 +2495,7 @@
         <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV11" t="n">
         <v>14</v>
@@ -2446,13 +2513,13 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
         <v>19</v>
       </c>
       <c r="BC11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
         <v>23</v>
@@ -2583,19 +2650,19 @@
         <v>16</v>
       </c>
       <c r="AL12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM12" t="n">
         <v>8</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>19</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ12" t="n">
         <v>5</v>
@@ -2619,10 +2686,10 @@
         <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2777,7 +2844,7 @@
         <v>26</v>
       </c>
       <c r="AP13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ13" t="n">
         <v>25</v>
@@ -2789,13 +2856,13 @@
         <v>20</v>
       </c>
       <c r="AT13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -2860,52 +2927,52 @@
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="J14" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L14" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.377</v>
+        <v>0.38</v>
       </c>
       <c r="O14" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="P14" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="Q14" t="n">
         <v>0.766</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S14" t="n">
-        <v>31.4</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="V14" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W14" t="n">
         <v>8.6</v>
       </c>
       <c r="X14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
         <v>4.4</v>
@@ -2917,22 +2984,22 @@
         <v>22.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.1</v>
+        <v>107.6</v>
       </c>
       <c r="AC14" t="n">
         <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>29</v>
@@ -2941,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2962,13 +3029,13 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2983,7 +3050,7 @@
         <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
@@ -2998,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3144,10 +3211,10 @@
         <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS15" t="n">
         <v>28</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
@@ -3302,7 +3369,7 @@
         <v>14</v>
       </c>
       <c r="AI16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ16" t="n">
         <v>13</v>
@@ -3323,16 +3390,16 @@
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ16" t="n">
         <v>29</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT16" t="n">
         <v>24</v>
@@ -3353,7 +3420,7 @@
         <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E17" t="n">
         <v>21</v>
       </c>
       <c r="F17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>0.477</v>
+        <v>0.467</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,7 +3476,7 @@
         <v>36.7</v>
       </c>
       <c r="J17" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K17" t="n">
         <v>0.449</v>
@@ -3421,31 +3488,31 @@
         <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O17" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P17" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R17" t="n">
         <v>12.4</v>
       </c>
       <c r="S17" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="U17" t="n">
         <v>21.2</v>
       </c>
       <c r="V17" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
         <v>7.1</v>
@@ -3457,16 +3524,16 @@
         <v>4.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,13 +3542,13 @@
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
         <v>15</v>
@@ -3499,25 +3566,25 @@
         <v>23</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
         <v>9</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AT17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU17" t="n">
         <v>12</v>
@@ -3532,7 +3599,7 @@
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3736,7 @@
         <v>14</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK18" t="n">
         <v>28</v>
@@ -3678,16 +3745,16 @@
         <v>21</v>
       </c>
       <c r="AM18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN18" t="n">
         <v>22</v>
       </c>
       <c r="AO18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ18" t="n">
         <v>17</v>
@@ -3699,10 +3766,10 @@
         <v>18</v>
       </c>
       <c r="AT18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV18" t="n">
         <v>15</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-3.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3860,10 +3927,10 @@
         <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO19" t="n">
         <v>8</v>
@@ -3908,7 +3975,7 @@
         <v>14</v>
       </c>
       <c r="BC19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -4039,7 +4106,7 @@
         <v>9</v>
       </c>
       <c r="AL20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM20" t="n">
         <v>12</v>
@@ -4048,7 +4115,7 @@
         <v>3</v>
       </c>
       <c r="AO20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>25</v>
@@ -4060,7 +4127,7 @@
         <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT20" t="n">
         <v>29</v>
@@ -4072,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="n">
         <v>23</v>
@@ -4081,7 +4148,7 @@
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA20" t="n">
         <v>13</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -4197,16 +4264,16 @@
         <v>-3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH21" t="n">
         <v>24</v>
@@ -4254,7 +4321,7 @@
         <v>22</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4272,7 +4339,7 @@
         <v>6</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4461,7 @@
         <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ22" t="n">
         <v>11</v>
@@ -4412,13 +4479,13 @@
         <v>11</v>
       </c>
       <c r="AO22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP22" t="n">
         <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -4483,103 +4550,103 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E23" t="n">
         <v>33</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.786</v>
+        <v>0.805</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.1</v>
+        <v>36.3</v>
       </c>
       <c r="J23" t="n">
-        <v>78.5</v>
+        <v>78.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L23" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="M23" t="n">
         <v>26</v>
       </c>
       <c r="N23" t="n">
-        <v>0.401</v>
+        <v>0.403</v>
       </c>
       <c r="O23" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P23" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="Q23" t="n">
         <v>0.719</v>
       </c>
       <c r="R23" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="T23" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
       <c r="U23" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="V23" t="n">
         <v>14.1</v>
       </c>
       <c r="W23" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z23" t="n">
         <v>20.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>101.8</v>
+        <v>102.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH23" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
         <v>8</v>
@@ -4597,7 +4664,7 @@
         <v>12</v>
       </c>
       <c r="AP23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4609,7 +4676,7 @@
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU23" t="n">
         <v>28</v>
@@ -4618,13 +4685,13 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX23" t="n">
         <v>4</v>
       </c>
       <c r="AY23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ23" t="n">
         <v>8</v>
@@ -4633,10 +4700,10 @@
         <v>8</v>
       </c>
       <c r="BB23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
         <v>17</v>
@@ -4764,7 +4831,7 @@
         <v>14</v>
       </c>
       <c r="AK24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL24" t="n">
         <v>28</v>
@@ -4776,10 +4843,10 @@
         <v>27</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ24" t="n">
         <v>27</v>
@@ -4791,7 +4858,7 @@
         <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU24" t="n">
         <v>15</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4998,7 @@
         <v>14</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG25" t="n">
         <v>13</v>
@@ -4970,7 +5037,7 @@
         <v>27</v>
       </c>
       <c r="AS25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.61</v>
+        <v>0.595</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J26" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="L26" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M26" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O26" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="P26" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.767</v>
+        <v>0.764</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
@@ -5077,10 +5144,10 @@
         <v>27.8</v>
       </c>
       <c r="T26" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U26" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V26" t="n">
         <v>12.8</v>
@@ -5095,43 +5162,43 @@
         <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>9</v>
       </c>
       <c r="AF26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AL26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM26" t="n">
         <v>10</v>
@@ -5140,13 +5207,13 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP26" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,10 +5222,10 @@
         <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5167,22 +5234,22 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA26" t="n">
         <v>11</v>
       </c>
       <c r="BB26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5362,7 @@
         <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG27" t="n">
         <v>27</v>
@@ -5304,7 +5371,7 @@
         <v>5</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="n">
         <v>12</v>
@@ -5313,7 +5380,7 @@
         <v>24</v>
       </c>
       <c r="AL27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM27" t="n">
         <v>16</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5486,7 +5553,7 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ28" t="n">
         <v>17</v>
@@ -5510,13 +5577,13 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
         <v>22</v>
@@ -5546,7 +5613,7 @@
         <v>21</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>22</v>
@@ -5668,13 +5735,13 @@
         <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
         <v>18</v>
@@ -5686,10 +5753,10 @@
         <v>10</v>
       </c>
       <c r="AO29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5947,7 @@
         <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
         <v>16</v>
@@ -5895,10 +5962,10 @@
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ30" t="n">
         <v>25</v>
@@ -5907,10 +5974,10 @@
         <v>3</v>
       </c>
       <c r="BB30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E31" t="n">
         <v>9</v>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G31" t="n">
-        <v>0.214</v>
+        <v>0.22</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5966,73 +6033,73 @@
         <v>5</v>
       </c>
       <c r="M31" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="N31" t="n">
         <v>0.317</v>
       </c>
       <c r="O31" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P31" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.756</v>
+        <v>0.753</v>
       </c>
       <c r="R31" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S31" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T31" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="U31" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V31" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W31" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X31" t="n">
         <v>4.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>94.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.7</v>
+        <v>-6.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
       </c>
       <c r="AF31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG31" t="n">
         <v>28</v>
       </c>
-      <c r="AG31" t="n">
-        <v>29</v>
-      </c>
       <c r="AH31" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ31" t="n">
         <v>10</v>
@@ -6056,7 +6123,7 @@
         <v>28</v>
       </c>
       <c r="AQ31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR31" t="n">
         <v>10</v>
@@ -6068,7 +6135,7 @@
         <v>25</v>
       </c>
       <c r="AU31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV31" t="n">
         <v>9</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-22-2008-09</t>
+          <t>2009-01-22</t>
         </is>
       </c>
     </row>
